--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R2" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +917,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R4" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -971,17 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,14 +819,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R3" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667517</v>
+        <v>124667512</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +930,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717140</v>
+        <v>717180</v>
       </c>
       <c r="R4" t="n">
-        <v>7205856</v>
+        <v>7205616</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667415</v>
+        <v>124667512</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716724</v>
+        <v>717180</v>
       </c>
       <c r="R2" t="n">
-        <v>7205635</v>
+        <v>7205616</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +779,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R3" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,14 +934,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R4" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R2" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -779,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -790,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667415</v>
+        <v>124667512</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,37 +802,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716724</v>
+        <v>717180</v>
       </c>
       <c r="R3" t="n">
-        <v>7205635</v>
+        <v>7205616</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R4" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -976,12 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667517</v>
+        <v>124667512</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717140</v>
+        <v>717180</v>
       </c>
       <c r="R2" t="n">
-        <v>7205856</v>
+        <v>7205616</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B3" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +806,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -819,14 +823,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -835,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R3" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667512</v>
+        <v>124667415</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717180</v>
+        <v>716724</v>
       </c>
       <c r="R2" t="n">
-        <v>7205616</v>
+        <v>7205635</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -890,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667415</v>
+        <v>124667512</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,37 +913,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716724</v>
+        <v>717180</v>
       </c>
       <c r="R4" t="n">
-        <v>7205635</v>
+        <v>7205616</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R2" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,17 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R3" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,12 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667517</v>
+        <v>124667512</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717140</v>
+        <v>717180</v>
       </c>
       <c r="R2" t="n">
-        <v>7205856</v>
+        <v>7205616</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -897,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,14 +934,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R4" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R3" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R4" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -976,12 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667512</v>
+        <v>124667415</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717180</v>
+        <v>716724</v>
       </c>
       <c r="R2" t="n">
-        <v>7205616</v>
+        <v>7205635</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667415</v>
+        <v>124667512</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,37 +913,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716724</v>
+        <v>717180</v>
       </c>
       <c r="R4" t="n">
-        <v>7205635</v>
+        <v>7205616</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,17 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R2" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -745,17 +750,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,39 +802,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R3" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -861,12 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667517</v>
+        <v>124667512</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,10 +708,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717140</v>
+        <v>717180</v>
       </c>
       <c r="R2" t="n">
-        <v>7205856</v>
+        <v>7205616</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -886,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Andreas Bernhold, Isak Vahlström</t>
+          <t>Isak Vahlström, Andreas Bernhold</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -897,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -930,14 +934,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R4" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,34 +806,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R3" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -860,17 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +890,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Andreas Bernhold</t>
+          <t>Andreas Bernhold, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,39 +917,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R4" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -976,12 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124667517</v>
+        <v>124667415</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,39 +806,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717140</v>
+        <v>716724</v>
       </c>
       <c r="R3" t="n">
-        <v>7205856</v>
+        <v>7205635</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,12 +860,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667415</v>
+        <v>124667517</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,34 +917,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rismyrliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716724</v>
+        <v>717140</v>
       </c>
       <c r="R4" t="n">
-        <v>7205635</v>
+        <v>7205856</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -971,17 +976,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal björk</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 29312-2023 artfynd.xlsx
+++ b/artfynd/A 29312-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124667512</v>
+        <v>124667517</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,14 +708,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>717180</v>
+        <v>717140</v>
       </c>
       <c r="R2" t="n">
-        <v>7205616</v>
+        <v>7205856</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -793,7 +789,7 @@
         <v>124667415</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -901,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124667517</v>
+        <v>124667512</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +913,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -934,10 +930,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -946,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717140</v>
+        <v>717180</v>
       </c>
       <c r="R4" t="n">
-        <v>7205856</v>
+        <v>7205616</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
